--- a/Acuerdo_Proveedores_CENASE.xlsx
+++ b/Acuerdo_Proveedores_CENASE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\NATHALY VARELA\2026\PROVEEDORES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D2B965F-46EA-4312-BB15-108F8D9AD975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A2BF1C7-7333-4AE4-A791-2F860405F2DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -391,7 +391,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -459,8 +459,19 @@
       <name val="Verdana"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -491,6 +502,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -544,59 +561,44 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -605,20 +607,35 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -994,7 +1011,7 @@
       <c r="B2" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="5" t="s">
         <v>61</v>
       </c>
       <c r="D2" s="2" t="s">
@@ -1003,10 +1020,10 @@
       <c r="E2" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="6" t="s">
         <v>64</v>
       </c>
       <c r="H2" s="2" t="s">
@@ -1017,18 +1034,18 @@
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="C3" s="13" t="s">
         <v>75</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
-      <c r="F3" s="30" t="s">
+      <c r="F3" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="G3" s="30" t="s">
+      <c r="G3" s="13" t="s">
         <v>78</v>
       </c>
       <c r="H3" s="2"/>
@@ -2225,31 +2242,31 @@
   <dimension ref="A3:K102"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="7" width="11" style="14" customWidth="1"/>
-    <col min="8" max="8" width="12.75" style="14" customWidth="1"/>
+    <col min="1" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.75" customWidth="1"/>
     <col min="10" max="11" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:11" ht="16.7" customHeight="1">
-      <c r="A3" s="12" t="s">
+    <row r="3" spans="1:11" s="33" customFormat="1" ht="16.7" customHeight="1">
+      <c r="A3" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="J3" t="s">
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="J3" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="33" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15" hidden="1" customHeight="1">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="7" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="3">
@@ -2273,16 +2290,16 @@
       </c>
     </row>
     <row r="6" spans="1:11" ht="15" customHeight="1">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
+      <c r="B6" s="29"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="29"/>
       <c r="J6" t="s">
         <v>14</v>
       </c>
@@ -2292,16 +2309,16 @@
       </c>
     </row>
     <row r="7" spans="1:11" ht="57" customHeight="1">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="29"/>
       <c r="J7" t="s">
         <v>15</v>
       </c>
@@ -2311,17 +2328,17 @@
       </c>
     </row>
     <row r="8" spans="1:11" ht="52.5" customHeight="1">
-      <c r="A8" s="15" t="str">
+      <c r="A8" s="29" t="str">
         <f>IF($K$4="","B. Seleccione un N° de proveedor en B2.","B. La compañía "&amp;$K$4&amp;", con RUC "&amp;$K$5&amp;", debida y legalmente representada por "&amp;$K$6&amp;", cuya personería se acredita con el nombramiento que se adjunta al presente instrumento en calidad de documento habilitante, parte a la que para los efectos del presente contrato se la denominará en lo sucesivo como “EL PROVEEDOR”")</f>
         <v>B. La compañía NATHALY VARELA , con RUC 0927255406001, debida y legalmente representada por NATHALY VARELA , cuya personería se acredita con el nombramiento que se adjunta al presente instrumento en calidad de documento habilitante, parte a la que para los efectos del presente contrato se la denominará en lo sucesivo como “EL PROVEEDOR”</v>
       </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
       <c r="J8" t="s">
         <v>16</v>
       </c>
@@ -2331,16 +2348,16 @@
       </c>
     </row>
     <row r="9" spans="1:11" ht="57" customHeight="1">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="29"/>
+      <c r="H9" s="29"/>
       <c r="J9" t="s">
         <v>17</v>
       </c>
@@ -2350,16 +2367,16 @@
       </c>
     </row>
     <row r="10" spans="1:11" ht="36" customHeight="1">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="29"/>
       <c r="J10" t="s">
         <v>18</v>
       </c>
@@ -2369,700 +2386,739 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="29"/>
+      <c r="H11" s="29"/>
     </row>
     <row r="12" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
+      <c r="B12" s="29"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="29"/>
+      <c r="H12" s="29"/>
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="29"/>
+      <c r="H13" s="29"/>
     </row>
     <row r="14" spans="1:11" ht="67.5" customHeight="1">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
+      <c r="B14" s="29"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+      <c r="H14" s="29"/>
     </row>
     <row r="15" spans="1:11" ht="15" customHeight="1">
-      <c r="A15" s="15" t="s">
+      <c r="A15" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
     </row>
     <row r="16" spans="1:11" ht="26.25" customHeight="1">
-      <c r="A16" s="15" t="s">
+      <c r="A16" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="29"/>
+      <c r="H16" s="29"/>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1">
-      <c r="A17" s="15" t="s">
+      <c r="A17" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="29"/>
+      <c r="H17" s="29"/>
     </row>
     <row r="18" spans="1:8" ht="24" customHeight="1">
-      <c r="A18" s="15" t="s">
+      <c r="A18" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
+      <c r="B18" s="29"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="29"/>
+      <c r="H18" s="29"/>
     </row>
     <row r="19" spans="1:8" ht="55.5" customHeight="1">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
+      <c r="B19" s="29"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="29"/>
     </row>
     <row r="20" spans="1:8" ht="40.5" customHeight="1">
-      <c r="A20" s="15" t="s">
+      <c r="A20" s="29" t="s">
         <v>71</v>
       </c>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
+      <c r="B20" s="29"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="29"/>
     </row>
     <row r="21" spans="1:8" ht="15" customHeight="1">
-      <c r="A21" s="21" t="s">
+      <c r="A21" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="21"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="21"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1">
-      <c r="A22" s="22" t="s">
+      <c r="A22" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="B22" s="22"/>
-      <c r="C22" s="23" t="str">
+      <c r="B22" s="28"/>
+      <c r="C22" s="19" t="str">
         <f>$K7</f>
         <v xml:space="preserve">23 AVA Y FRANCISCO SEGURA </v>
       </c>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="22"/>
-      <c r="C23" s="23" t="str">
+      <c r="B23" s="28"/>
+      <c r="C23" s="19" t="str">
         <f>$K8</f>
         <v>0989829904</v>
       </c>
-      <c r="D23" s="23"/>
-      <c r="E23" s="23"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
     </row>
     <row r="24" spans="1:8" ht="21.6" customHeight="1">
-      <c r="A24" s="22" t="s">
+      <c r="A24" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="B24" s="22"/>
-      <c r="C24" s="23" t="str">
+      <c r="B24" s="28"/>
+      <c r="C24" s="19" t="str">
         <f>$K9</f>
         <v>NATHALYCOM@MSN.COM</v>
       </c>
-      <c r="D24" s="23"/>
-      <c r="E24" s="23"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1">
-      <c r="A25" s="22" t="s">
+      <c r="A25" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="B25" s="22"/>
-      <c r="C25" s="23" t="str">
+      <c r="B25" s="28"/>
+      <c r="C25" s="19" t="str">
         <f>$K10</f>
         <v xml:space="preserve">ROCIO BENAVIDES </v>
       </c>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
     </row>
     <row r="26" spans="1:8" ht="15" customHeight="1">
-      <c r="A26" s="20"/>
-      <c r="B26" s="20"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="20"/>
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
     </row>
     <row r="27" spans="1:8" ht="15" customHeight="1">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="21"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="20"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
     </row>
     <row r="28" spans="1:8" ht="15" customHeight="1">
-      <c r="A28" s="22" t="s">
+      <c r="A28" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="22"/>
-      <c r="C28" s="23" t="s">
+      <c r="B28" s="28"/>
+      <c r="C28" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="20"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
     </row>
     <row r="29" spans="1:8" ht="15" customHeight="1">
-      <c r="A29" s="22" t="s">
+      <c r="A29" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="B29" s="22"/>
-      <c r="C29" s="23" t="s">
+      <c r="B29" s="28"/>
+      <c r="C29" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="D29" s="23"/>
-      <c r="E29" s="23"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
     </row>
     <row r="30" spans="1:8" ht="15" customHeight="1">
-      <c r="A30" s="22" t="s">
+      <c r="A30" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="B30" s="22"/>
-      <c r="C30" s="23" t="s">
+      <c r="B30" s="28"/>
+      <c r="C30" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="D30" s="23"/>
-      <c r="E30" s="23"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="20"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="22" t="s">
+      <c r="A31" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="B31" s="22"/>
-      <c r="C31" s="23" t="s">
+      <c r="B31" s="28"/>
+      <c r="C31" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="D31" s="23"/>
-      <c r="E31" s="23"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="20"/>
-      <c r="B32" s="20"/>
-      <c r="C32" s="20"/>
-      <c r="D32" s="20"/>
+      <c r="A32" s="11"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
     </row>
     <row r="33" spans="1:8" ht="24" customHeight="1">
-      <c r="A33" s="16" t="s">
+      <c r="A33" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="B33" s="16"/>
-      <c r="C33" s="16"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="16"/>
-      <c r="H33" s="16"/>
+      <c r="B33" s="26"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
+      <c r="H33" s="26"/>
     </row>
     <row r="34" spans="1:8" ht="15" customHeight="1">
-      <c r="A34" s="32"/>
-      <c r="B34" s="32"/>
-      <c r="C34" s="32"/>
-      <c r="D34" s="32"/>
-      <c r="E34" s="32"/>
-      <c r="F34" s="32"/>
-      <c r="G34" s="32"/>
-      <c r="H34" s="32"/>
+      <c r="A34" s="8"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
     </row>
     <row r="35" spans="1:8" ht="15" customHeight="1">
-      <c r="B35" s="32"/>
-      <c r="C35" s="32"/>
-      <c r="D35" s="32"/>
-      <c r="E35" s="32"/>
-      <c r="F35" s="32"/>
-      <c r="G35" s="32"/>
-      <c r="H35" s="32"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
     </row>
     <row r="36" spans="1:8" ht="15" customHeight="1">
-      <c r="A36" s="33"/>
-      <c r="B36" s="32"/>
-      <c r="C36" s="32"/>
-      <c r="D36" s="32"/>
-      <c r="E36" s="32"/>
-      <c r="F36" s="32"/>
-      <c r="G36" s="32"/>
-      <c r="H36" s="32"/>
+      <c r="A36" s="15"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
     </row>
     <row r="37" spans="1:8" ht="15" customHeight="1">
-      <c r="A37" s="33" t="s">
+      <c r="A37" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="B37" s="32"/>
-      <c r="C37" s="32"/>
-      <c r="D37" s="32"/>
-      <c r="E37" s="32"/>
-      <c r="F37" s="32"/>
-      <c r="G37" s="32"/>
-      <c r="H37" s="32"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="8"/>
     </row>
     <row r="38" spans="1:8" ht="15" customHeight="1">
-      <c r="A38" s="16" t="s">
+      <c r="A38" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="B38" s="16"/>
-      <c r="C38" s="16"/>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="16"/>
-      <c r="G38" s="16"/>
-      <c r="H38" s="16"/>
+      <c r="B38" s="26"/>
+      <c r="C38" s="26"/>
+      <c r="D38" s="26"/>
+      <c r="E38" s="26"/>
+      <c r="F38" s="26"/>
+      <c r="G38" s="26"/>
+      <c r="H38" s="26"/>
     </row>
     <row r="39" spans="1:8" ht="82.5" customHeight="1">
-      <c r="A39" s="6" t="s">
+      <c r="A39" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="B39" s="16"/>
-      <c r="C39" s="16"/>
-      <c r="D39" s="16"/>
-      <c r="E39" s="16"/>
-      <c r="F39" s="16"/>
-      <c r="G39" s="16"/>
-      <c r="H39" s="16"/>
+      <c r="B39" s="26"/>
+      <c r="C39" s="26"/>
+      <c r="D39" s="26"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="26"/>
+      <c r="G39" s="26"/>
+      <c r="H39" s="26"/>
     </row>
     <row r="40" spans="1:8" ht="43.5" customHeight="1">
-      <c r="A40" s="16" t="s">
+      <c r="A40" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="B40" s="16"/>
-      <c r="C40" s="16"/>
-      <c r="D40" s="16"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="16"/>
-      <c r="G40" s="16"/>
-      <c r="H40" s="16"/>
+      <c r="B40" s="26"/>
+      <c r="C40" s="26"/>
+      <c r="D40" s="26"/>
+      <c r="E40" s="26"/>
+      <c r="F40" s="26"/>
+      <c r="G40" s="26"/>
+      <c r="H40" s="26"/>
     </row>
     <row r="41" spans="1:8" ht="108" customHeight="1">
-      <c r="A41" s="16" t="s">
+      <c r="A41" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="B41" s="16"/>
-      <c r="C41" s="16"/>
-      <c r="D41" s="16"/>
-      <c r="E41" s="16"/>
-      <c r="F41" s="16"/>
-      <c r="G41" s="16"/>
-      <c r="H41" s="16"/>
+      <c r="B41" s="26"/>
+      <c r="C41" s="26"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="26"/>
+      <c r="F41" s="26"/>
+      <c r="G41" s="26"/>
+      <c r="H41" s="26"/>
     </row>
     <row r="42" spans="1:8" ht="28.5" customHeight="1">
-      <c r="A42" s="16" t="s">
+      <c r="A42" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="B42" s="16"/>
-      <c r="C42" s="16"/>
-      <c r="D42" s="16"/>
-      <c r="E42" s="16"/>
-      <c r="F42" s="16"/>
-      <c r="G42" s="16"/>
-      <c r="H42" s="16"/>
+      <c r="B42" s="26"/>
+      <c r="C42" s="26"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="26"/>
+      <c r="G42" s="26"/>
+      <c r="H42" s="26"/>
     </row>
     <row r="44" spans="1:8" ht="15" customHeight="1">
-      <c r="A44" s="7" t="s">
+      <c r="A44" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7" t="s">
+      <c r="B44" s="25"/>
+      <c r="C44" s="25"/>
+      <c r="D44" s="25"/>
+      <c r="E44" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="F44" s="7"/>
-      <c r="G44" s="7"/>
-      <c r="H44" s="7"/>
-    </row>
-    <row r="48" spans="1:8">
-      <c r="B48"/>
+      <c r="F44" s="25"/>
+      <c r="G44" s="25"/>
+      <c r="H44" s="25"/>
     </row>
     <row r="50" spans="1:8" ht="15" customHeight="1">
-      <c r="A50" s="7" t="s">
+      <c r="A50" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="B50" s="7"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="7" t="str">
+      <c r="B50" s="25"/>
+      <c r="C50" s="25"/>
+      <c r="D50" s="25"/>
+      <c r="E50" s="25" t="str">
         <f>IF($K$6="","NOMBRE DEL FIRMANTE",$K$6)</f>
         <v xml:space="preserve">NATHALY VARELA </v>
       </c>
-      <c r="F50" s="7"/>
-      <c r="G50" s="7"/>
-      <c r="H50" s="7"/>
+      <c r="F50" s="25"/>
+      <c r="G50" s="25"/>
+      <c r="H50" s="25"/>
     </row>
     <row r="52" spans="1:8">
-      <c r="A52" s="31"/>
+      <c r="A52" s="14"/>
     </row>
     <row r="53" spans="1:8">
-      <c r="A53" s="31"/>
+      <c r="A53" s="14"/>
     </row>
     <row r="54" spans="1:8">
-      <c r="A54" s="31"/>
+      <c r="A54" s="14"/>
     </row>
     <row r="55" spans="1:8">
-      <c r="A55" s="31"/>
+      <c r="A55" s="14"/>
     </row>
     <row r="56" spans="1:8">
-      <c r="A56" s="31"/>
+      <c r="A56" s="14"/>
     </row>
     <row r="57" spans="1:8">
-      <c r="A57" s="31"/>
+      <c r="A57" s="14"/>
     </row>
     <row r="58" spans="1:8">
-      <c r="A58" s="31"/>
+      <c r="A58" s="14"/>
     </row>
     <row r="59" spans="1:8">
-      <c r="A59" s="31"/>
+      <c r="A59" s="14"/>
     </row>
     <row r="60" spans="1:8">
-      <c r="A60" s="31"/>
+      <c r="A60" s="14"/>
     </row>
     <row r="61" spans="1:8">
-      <c r="A61" s="31"/>
+      <c r="A61" s="14"/>
     </row>
     <row r="62" spans="1:8">
-      <c r="A62" s="31"/>
+      <c r="A62" s="14"/>
     </row>
     <row r="63" spans="1:8">
-      <c r="A63" s="31"/>
+      <c r="A63" s="14"/>
     </row>
     <row r="64" spans="1:8">
-      <c r="A64" s="31"/>
+      <c r="A64" s="14"/>
     </row>
     <row r="65" spans="1:8">
-      <c r="A65" s="31"/>
+      <c r="A65" s="14"/>
     </row>
     <row r="66" spans="1:8">
-      <c r="A66" s="31"/>
+      <c r="A66" s="14"/>
     </row>
     <row r="67" spans="1:8">
-      <c r="A67" s="31"/>
+      <c r="A67" s="14"/>
     </row>
     <row r="68" spans="1:8">
-      <c r="A68" s="31"/>
+      <c r="A68" s="14"/>
     </row>
     <row r="69" spans="1:8">
-      <c r="A69" s="33"/>
+      <c r="A69" s="15"/>
     </row>
     <row r="70" spans="1:8" ht="15" customHeight="1">
-      <c r="A70" s="17" t="s">
+      <c r="A70" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="B70" s="17"/>
-      <c r="C70" s="17"/>
-      <c r="D70" s="17"/>
-      <c r="E70" s="17"/>
-      <c r="F70" s="17"/>
-      <c r="G70" s="17"/>
-      <c r="H70" s="17"/>
+      <c r="B70" s="22"/>
+      <c r="C70" s="22"/>
+      <c r="D70" s="22"/>
+      <c r="E70" s="22"/>
+      <c r="F70" s="22"/>
+      <c r="G70" s="22"/>
+      <c r="H70" s="22"/>
     </row>
     <row r="71" spans="1:8" ht="15" customHeight="1">
-      <c r="A71" s="24" t="s">
+      <c r="A71" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="B71" s="24"/>
-      <c r="C71" s="24"/>
-      <c r="D71" s="24"/>
-      <c r="E71" s="24"/>
-      <c r="F71" s="24"/>
-      <c r="G71" s="24"/>
-      <c r="H71" s="24"/>
+      <c r="B71" s="23"/>
+      <c r="C71" s="23"/>
+      <c r="D71" s="23"/>
+      <c r="E71" s="23"/>
+      <c r="F71" s="23"/>
+      <c r="G71" s="23"/>
+      <c r="H71" s="23"/>
     </row>
     <row r="72" spans="1:8" ht="91.5" customHeight="1">
-      <c r="A72" s="19" t="s">
+      <c r="A72" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="B72" s="19"/>
-      <c r="C72" s="19"/>
-      <c r="D72" s="19"/>
-      <c r="E72" s="19"/>
-      <c r="F72" s="19"/>
-      <c r="G72" s="19"/>
-      <c r="H72" s="19"/>
+      <c r="B72" s="16"/>
+      <c r="C72" s="16"/>
+      <c r="D72" s="16"/>
+      <c r="E72" s="16"/>
+      <c r="F72" s="16"/>
+      <c r="G72" s="16"/>
+      <c r="H72" s="16"/>
     </row>
     <row r="73" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A73" s="25"/>
-      <c r="B73" s="25"/>
-      <c r="C73" s="25"/>
-      <c r="D73" s="25"/>
-      <c r="E73" s="25"/>
-      <c r="F73" s="25"/>
-      <c r="G73" s="25"/>
-      <c r="H73" s="25"/>
+      <c r="A73" s="10"/>
+      <c r="B73" s="10"/>
+      <c r="C73" s="10"/>
+      <c r="D73" s="10"/>
+      <c r="E73" s="10"/>
+      <c r="F73" s="10"/>
+      <c r="G73" s="10"/>
+      <c r="H73" s="10"/>
     </row>
     <row r="74" spans="1:8" ht="15" customHeight="1">
-      <c r="A74" s="18" t="s">
+      <c r="A74" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="B74" s="18"/>
-      <c r="C74" s="18"/>
-      <c r="D74" s="18"/>
-      <c r="E74" s="18"/>
-      <c r="F74" s="18"/>
-      <c r="G74" s="18"/>
-      <c r="H74" s="18"/>
+      <c r="B74" s="24"/>
+      <c r="C74" s="24"/>
+      <c r="D74" s="24"/>
+      <c r="E74" s="24"/>
+      <c r="F74" s="24"/>
+      <c r="G74" s="24"/>
+      <c r="H74" s="24"/>
     </row>
     <row r="75" spans="1:8" ht="15" customHeight="1">
-      <c r="A75" s="26" t="s">
+      <c r="A75" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="B75" s="26"/>
-      <c r="C75" s="26"/>
-      <c r="D75" s="26"/>
-      <c r="E75" s="26"/>
-      <c r="F75" s="26"/>
-      <c r="G75" s="26"/>
-      <c r="H75" s="26"/>
+      <c r="B75" s="21"/>
+      <c r="C75" s="21"/>
+      <c r="D75" s="21"/>
+      <c r="E75" s="21"/>
+      <c r="F75" s="21"/>
+      <c r="G75" s="21"/>
+      <c r="H75" s="21"/>
     </row>
     <row r="76" spans="1:8" ht="39" customHeight="1">
-      <c r="A76" s="28" t="s">
+      <c r="A76" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="B76" s="28"/>
-      <c r="C76" s="28"/>
-      <c r="D76" s="28"/>
-      <c r="E76" s="28"/>
-      <c r="F76" s="28"/>
-      <c r="G76" s="28"/>
-      <c r="H76" s="28"/>
+      <c r="B76" s="20"/>
+      <c r="C76" s="20"/>
+      <c r="D76" s="20"/>
+      <c r="E76" s="20"/>
+      <c r="F76" s="20"/>
+      <c r="G76" s="20"/>
+      <c r="H76" s="20"/>
     </row>
     <row r="77" spans="1:8" ht="31.5" customHeight="1">
-      <c r="A77" s="28" t="s">
+      <c r="A77" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="B77" s="28"/>
-      <c r="C77" s="28"/>
-      <c r="D77" s="28"/>
-      <c r="E77" s="28"/>
-      <c r="F77" s="28"/>
-      <c r="G77" s="28"/>
-      <c r="H77" s="28"/>
+      <c r="B77" s="20"/>
+      <c r="C77" s="20"/>
+      <c r="D77" s="20"/>
+      <c r="E77" s="20"/>
+      <c r="F77" s="20"/>
+      <c r="G77" s="20"/>
+      <c r="H77" s="20"/>
     </row>
     <row r="78" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A78" s="29"/>
-      <c r="B78" s="29"/>
-      <c r="C78" s="29"/>
-      <c r="D78" s="29"/>
-      <c r="E78" s="29"/>
-      <c r="F78" s="29"/>
-      <c r="G78" s="29"/>
-      <c r="H78" s="29"/>
+      <c r="A78" s="12"/>
+      <c r="B78" s="12"/>
+      <c r="C78" s="12"/>
+      <c r="D78" s="12"/>
+      <c r="E78" s="12"/>
+      <c r="F78" s="12"/>
+      <c r="G78" s="12"/>
+      <c r="H78" s="12"/>
     </row>
     <row r="79" spans="1:8" ht="15" customHeight="1">
-      <c r="A79" s="26" t="s">
+      <c r="A79" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B79" s="26"/>
-      <c r="C79" s="26"/>
-      <c r="D79" s="26"/>
-      <c r="E79" s="26"/>
-      <c r="F79" s="26"/>
-      <c r="G79" s="26"/>
-      <c r="H79" s="26"/>
+      <c r="B79" s="21"/>
+      <c r="C79" s="21"/>
+      <c r="D79" s="21"/>
+      <c r="E79" s="21"/>
+      <c r="F79" s="21"/>
+      <c r="G79" s="21"/>
+      <c r="H79" s="21"/>
     </row>
     <row r="80" spans="1:8" ht="56.25" customHeight="1">
-      <c r="A80" s="28" t="s">
+      <c r="A80" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="B80" s="28"/>
-      <c r="C80" s="28"/>
-      <c r="D80" s="28"/>
-      <c r="E80" s="28"/>
-      <c r="F80" s="28"/>
-      <c r="G80" s="28"/>
-      <c r="H80" s="28"/>
+      <c r="B80" s="20"/>
+      <c r="C80" s="20"/>
+      <c r="D80" s="20"/>
+      <c r="E80" s="20"/>
+      <c r="F80" s="20"/>
+      <c r="G80" s="20"/>
+      <c r="H80" s="20"/>
     </row>
     <row r="81" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A81" s="28" t="s">
+      <c r="A81" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="B81" s="28"/>
-      <c r="C81" s="28"/>
-      <c r="D81" s="28"/>
-      <c r="E81" s="28"/>
-      <c r="F81" s="28"/>
-      <c r="G81" s="28"/>
-      <c r="H81" s="28"/>
+      <c r="B81" s="20"/>
+      <c r="C81" s="20"/>
+      <c r="D81" s="20"/>
+      <c r="E81" s="20"/>
+      <c r="F81" s="20"/>
+      <c r="G81" s="20"/>
+      <c r="H81" s="20"/>
     </row>
     <row r="82" spans="1:8" ht="15" customHeight="1">
-      <c r="A82" s="29"/>
-      <c r="B82" s="29"/>
-      <c r="C82" s="29"/>
-      <c r="D82" s="29"/>
-      <c r="E82" s="29"/>
-      <c r="F82" s="29"/>
-      <c r="G82" s="29"/>
-      <c r="H82" s="29"/>
+      <c r="A82" s="12"/>
+      <c r="B82" s="12"/>
+      <c r="C82" s="12"/>
+      <c r="D82" s="12"/>
+      <c r="E82" s="12"/>
+      <c r="F82" s="12"/>
+      <c r="G82" s="12"/>
+      <c r="H82" s="12"/>
     </row>
     <row r="83" spans="1:8" ht="15" customHeight="1">
-      <c r="A83" s="17" t="s">
+      <c r="A83" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="B83" s="17"/>
-      <c r="C83" s="17"/>
-      <c r="D83" s="17"/>
-      <c r="E83" s="17"/>
-      <c r="F83" s="17"/>
-      <c r="G83" s="17"/>
-      <c r="H83" s="17"/>
+      <c r="B83" s="22"/>
+      <c r="C83" s="22"/>
+      <c r="D83" s="22"/>
+      <c r="E83" s="22"/>
+      <c r="F83" s="22"/>
+      <c r="G83" s="22"/>
+      <c r="H83" s="22"/>
     </row>
     <row r="84" spans="1:8" ht="15" customHeight="1">
-      <c r="A84" s="27"/>
-      <c r="B84" s="27"/>
-      <c r="C84" s="27"/>
-      <c r="D84" s="27"/>
-      <c r="E84" s="27"/>
-      <c r="F84" s="27"/>
-      <c r="G84" s="27"/>
-      <c r="H84" s="27"/>
+      <c r="A84" s="9"/>
+      <c r="B84" s="9"/>
+      <c r="C84" s="9"/>
+      <c r="D84" s="9"/>
+      <c r="E84" s="9"/>
+      <c r="F84" s="9"/>
+      <c r="G84" s="9"/>
+      <c r="H84" s="9"/>
     </row>
     <row r="85" spans="1:8" ht="24" customHeight="1">
-      <c r="A85" s="19" t="s">
+      <c r="A85" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="B85" s="19"/>
-      <c r="C85" s="19"/>
-      <c r="D85" s="19"/>
-      <c r="E85" s="19"/>
-      <c r="F85" s="19"/>
-      <c r="G85" s="19"/>
-      <c r="H85" s="19"/>
+      <c r="B85" s="16"/>
+      <c r="C85" s="16"/>
+      <c r="D85" s="16"/>
+      <c r="E85" s="16"/>
+      <c r="F85" s="16"/>
+      <c r="G85" s="16"/>
+      <c r="H85" s="16"/>
     </row>
     <row r="86" spans="1:8" ht="12.75" customHeight="1">
-      <c r="A86" s="25"/>
-      <c r="B86" s="25"/>
-      <c r="C86" s="25"/>
-      <c r="D86" s="25"/>
-      <c r="E86" s="25"/>
-      <c r="F86" s="25"/>
-      <c r="G86" s="25"/>
-      <c r="H86" s="25"/>
+      <c r="A86" s="10"/>
+      <c r="B86" s="10"/>
+      <c r="C86" s="10"/>
+      <c r="D86" s="10"/>
+      <c r="E86" s="10"/>
+      <c r="F86" s="10"/>
+      <c r="G86" s="10"/>
+      <c r="H86" s="10"/>
     </row>
     <row r="87" spans="1:8" ht="334.5" customHeight="1">
-      <c r="A87" s="8" t="s">
+      <c r="A87" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="B87" s="19"/>
-      <c r="C87" s="19"/>
-      <c r="D87" s="19"/>
-      <c r="E87" s="19"/>
-      <c r="F87" s="19"/>
-      <c r="G87" s="19"/>
-      <c r="H87" s="19"/>
+      <c r="B87" s="16"/>
+      <c r="C87" s="16"/>
+      <c r="D87" s="16"/>
+      <c r="E87" s="16"/>
+      <c r="F87" s="16"/>
+      <c r="G87" s="16"/>
+      <c r="H87" s="16"/>
     </row>
     <row r="88" spans="1:8" ht="14.25" customHeight="1">
       <c r="A88" s="4"/>
-      <c r="B88" s="25"/>
-      <c r="C88" s="25"/>
-      <c r="D88" s="25"/>
-      <c r="E88" s="25"/>
-      <c r="F88" s="25"/>
-      <c r="G88" s="25"/>
-      <c r="H88" s="25"/>
+      <c r="B88" s="10"/>
+      <c r="C88" s="10"/>
+      <c r="D88" s="10"/>
+      <c r="E88" s="10"/>
+      <c r="F88" s="10"/>
+      <c r="G88" s="10"/>
+      <c r="H88" s="10"/>
     </row>
     <row r="89" spans="1:8" ht="36" customHeight="1">
-      <c r="A89" s="19" t="s">
+      <c r="A89" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="B89" s="19"/>
-      <c r="C89" s="19"/>
-      <c r="D89" s="19"/>
-      <c r="E89" s="19"/>
-      <c r="F89" s="19"/>
-      <c r="G89" s="19"/>
-      <c r="H89" s="19"/>
+      <c r="B89" s="16"/>
+      <c r="C89" s="16"/>
+      <c r="D89" s="16"/>
+      <c r="E89" s="16"/>
+      <c r="F89" s="16"/>
+      <c r="G89" s="16"/>
+      <c r="H89" s="16"/>
     </row>
     <row r="92" spans="1:8">
-      <c r="A92" s="33" t="s">
+      <c r="A92" s="15" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="102" spans="1:1">
-      <c r="A102" s="31"/>
+      <c r="A102" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="58">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="A39:H39"/>
+    <mergeCell ref="A40:H40"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="E50:H50"/>
+    <mergeCell ref="A70:H70"/>
+    <mergeCell ref="A81:H81"/>
+    <mergeCell ref="A83:H83"/>
+    <mergeCell ref="A71:H71"/>
+    <mergeCell ref="A72:H72"/>
+    <mergeCell ref="A74:H74"/>
+    <mergeCell ref="A75:H75"/>
+    <mergeCell ref="A76:H76"/>
     <mergeCell ref="A85:H85"/>
     <mergeCell ref="A87:H87"/>
     <mergeCell ref="A89:H89"/>
@@ -3079,48 +3135,6 @@
     <mergeCell ref="A77:H77"/>
     <mergeCell ref="A79:H79"/>
     <mergeCell ref="A80:H80"/>
-    <mergeCell ref="A81:H81"/>
-    <mergeCell ref="A83:H83"/>
-    <mergeCell ref="A71:H71"/>
-    <mergeCell ref="A72:H72"/>
-    <mergeCell ref="A74:H74"/>
-    <mergeCell ref="A75:H75"/>
-    <mergeCell ref="A76:H76"/>
-    <mergeCell ref="A44:D44"/>
-    <mergeCell ref="E44:H44"/>
-    <mergeCell ref="A50:D50"/>
-    <mergeCell ref="E50:H50"/>
-    <mergeCell ref="A70:H70"/>
-    <mergeCell ref="A38:H38"/>
-    <mergeCell ref="A39:H39"/>
-    <mergeCell ref="A40:H40"/>
-    <mergeCell ref="A41:H41"/>
-    <mergeCell ref="A42:H42"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A33:H33"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="A17:H17"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A6:H6"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A9:H9"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="B4" xr:uid="{00000000-0002-0000-0100-000000000000}">
@@ -3154,64 +3168,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
+      <c r="B6" s="30"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="6">
